--- a/tools/importer/reports/import-rinvoq-ra.report.xlsx
+++ b/tools/importer/reports/import-rinvoq-ra.report.xlsx
@@ -73,7 +73,7 @@
     <t>rinvoq-ra</t>
   </si>
   <si>
-    <t>2026-06-19T04:41:06.426Z</t>
+    <t>2026-06-19T08:27:37.463Z</t>
   </si>
   <si>
     <t>RINVOQ® (upadacitinib) for Rheumatoid Arthritis</t>
